--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -102,10 +102,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -117,6 +117,87 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -125,7 +206,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -133,29 +214,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -170,6 +236,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -177,28 +244,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -207,54 +253,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,6 +269,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -281,25 +407,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,79 +419,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,61 +449,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,17 +460,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -485,24 +474,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,8 +496,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -542,6 +513,35 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -568,145 +568,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -34,7 +34,7 @@
     <t>TITLE</t>
   </si>
   <si>
-    <t>PerituneMaterial_RainDrop_loop</t>
+    <t>Field3</t>
   </si>
   <si>
     <t>MAINMENU</t>
@@ -46,13 +46,10 @@
     <t>TACTICS1</t>
   </si>
   <si>
-    <t>PerituneMaterial_Firmament3_Calm_loop</t>
-  </si>
-  <si>
     <t>TACTICS2</t>
   </si>
   <si>
-    <t>PerituneMaterial_Firmament3_Active_loop</t>
+    <t>Battle5</t>
   </si>
   <si>
     <t>TACTICS3</t>
@@ -102,10 +99,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -117,73 +114,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -197,26 +157,88 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -228,33 +250,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,13 +266,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,169 +398,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -478,6 +475,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -489,39 +495,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -560,6 +533,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -568,145 +565,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1123,13 +1120,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1137,10 +1134,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -1154,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1171,16 +1168,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
         <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1188,10 +1185,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
         <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -1202,10 +1199,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -1216,10 +1213,10 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -1230,10 +1227,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
         <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -1244,10 +1241,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
@@ -1258,10 +1255,10 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
         <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>Id</t>
   </si>
@@ -34,7 +34,7 @@
     <t>TITLE</t>
   </si>
   <si>
-    <t>Field3</t>
+    <t>libra_rebirth_arrange</t>
   </si>
   <si>
     <t>MAINMENU</t>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>TACTICS1</t>
+  </si>
+  <si>
+    <t>all_out_attack</t>
   </si>
   <si>
     <t>TACTICS2</t>
@@ -99,9 +102,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -113,6 +116,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -120,15 +153,70 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -142,111 +230,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -266,31 +269,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -302,13 +425,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -320,133 +443,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,15 +478,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -495,6 +489,54 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -518,45 +560,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -565,145 +568,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1112,7 +1115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1120,64 +1123,52 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1185,10 +1176,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -1199,10 +1190,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -1213,10 +1204,10 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -1227,10 +1218,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -1241,10 +1232,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
@@ -1255,10 +1246,10 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Id</t>
   </si>
@@ -25,6 +25,9 @@
     <t>FileName</t>
   </si>
   <si>
+    <t>Volume</t>
+  </si>
+  <si>
     <t>Loop</t>
   </si>
   <si>
@@ -37,10 +40,22 @@
     <t>libra_rebirth_arrange</t>
   </si>
   <si>
-    <t>MAINMENU</t>
-  </si>
-  <si>
-    <t>PerituneMaterial_Limpid_Water_loop</t>
+    <t>MAINMENU1</t>
+  </si>
+  <si>
+    <t>luminosite</t>
+  </si>
+  <si>
+    <t>MAINMENU2</t>
+  </si>
+  <si>
+    <t>kono_sekai_no_hate_e</t>
+  </si>
+  <si>
+    <t>MAINMENU3</t>
+  </si>
+  <si>
+    <t>sugiikuaki</t>
   </si>
   <si>
     <t>TACTICS1</t>
@@ -52,49 +67,97 @@
     <t>TACTICS2</t>
   </si>
   <si>
-    <t>Battle5</t>
+    <t>enemy_in_sight!</t>
   </si>
   <si>
     <t>TACTICS3</t>
   </si>
   <si>
-    <t>PerituneMaterial_Grief_inst_loop</t>
+    <t>Halfway Hard-boiled Boys(2015edit)</t>
   </si>
   <si>
     <t>TACTICS4</t>
   </si>
   <si>
-    <t>PerituneMaterial_Grief_loop</t>
+    <t>resurrection</t>
+  </si>
+  <si>
+    <t>TACTICS5</t>
+  </si>
+  <si>
+    <t>foresight_22</t>
+  </si>
+  <si>
+    <t>TACTICS6</t>
+  </si>
+  <si>
+    <t>n_or_bs</t>
+  </si>
+  <si>
+    <t>TACTICS7</t>
+  </si>
+  <si>
+    <t>ladiyjye</t>
+  </si>
+  <si>
+    <t>TACTICS8</t>
+  </si>
+  <si>
+    <t>cumulonimbus</t>
+  </si>
+  <si>
+    <t>TACTICS9</t>
+  </si>
+  <si>
+    <t>yozakura</t>
+  </si>
+  <si>
+    <t>TACTICS10</t>
+  </si>
+  <si>
+    <t>sakura_seiten</t>
+  </si>
+  <si>
+    <t>TACTICS11</t>
+  </si>
+  <si>
+    <t>kazanebi</t>
+  </si>
+  <si>
+    <t>TACTICS12</t>
+  </si>
+  <si>
+    <t>wind_run_through</t>
+  </si>
+  <si>
+    <t>TACTICS13</t>
+  </si>
+  <si>
+    <t>n_or_kp</t>
+  </si>
+  <si>
+    <t>TACTICS14</t>
+  </si>
+  <si>
+    <t>moonless_night</t>
+  </si>
+  <si>
+    <t>TACTICS15</t>
+  </si>
+  <si>
+    <t>salvation</t>
   </si>
   <si>
     <t>BOSS1</t>
   </si>
   <si>
-    <t>PerituneMaterial_Cyber_Noir_loop</t>
-  </si>
-  <si>
-    <t>OPENING</t>
-  </si>
-  <si>
-    <t>EVENT1</t>
-  </si>
-  <si>
-    <t>PerituneMaterial_Dawning_Tale</t>
-  </si>
-  <si>
-    <t>EVENT2</t>
-  </si>
-  <si>
-    <t>PerituneMaterial_Limpid_Water_melodyoff_loop</t>
-  </si>
-  <si>
-    <t>ENDING</t>
-  </si>
-  <si>
-    <t>LAST_BOSS</t>
-  </si>
-  <si>
-    <t>UniqueGear_Kaibyaku_No_Ragnarok</t>
+    <t>amatias</t>
+  </si>
+  <si>
+    <t>BOSS2</t>
+  </si>
+  <si>
+    <t>debris_cloud_0</t>
   </si>
 </sst>
 </file>
@@ -102,10 +165,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -116,11 +179,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -131,46 +214,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -198,9 +252,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,14 +277,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -240,14 +294,23 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,13 +332,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,31 +428,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -323,133 +500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -502,30 +565,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -537,6 +576,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -560,6 +608,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -568,142 +631,142 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1062,15 +1125,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="4"/>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
     <col min="3" max="3" width="42.7272727272727" customWidth="1"/>
-    <col min="5" max="5" width="10.6363636363636" customWidth="1"/>
+    <col min="4" max="4" width="7.72727272727273" customWidth="1"/>
+    <col min="6" max="6" width="10.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1086,172 +1150,364 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>0.8</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>0.8</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:5">
       <c r="A4">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>0.8</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:5">
       <c r="A5">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>0.8</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
-        <v>5</v>
+        <v>1010</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
-        <v>6</v>
+        <v>1020</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>0.8</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
-        <v>11</v>
+        <v>1030</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>0.8</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
-        <v>12</v>
+        <v>1040</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="D9">
+        <v>0.8</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
-        <v>13</v>
+        <v>1050</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>0.8</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
-        <v>14</v>
+        <v>1060</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <v>0.8</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
-        <v>15</v>
+        <v>1070</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>27</v>
+      </c>
+      <c r="D12">
+        <v>0.8</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
-        <v>16</v>
+        <v>1080</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="b">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>0.8</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>1090</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14">
+        <v>0.8</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>1100</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15">
+        <v>0.8</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>1110</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16">
+        <v>0.8</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>1120</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17">
+        <v>0.8</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>1130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18">
+        <v>0.8</v>
+      </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>1140</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19">
+        <v>0.8</v>
+      </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>1150</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20">
+        <v>0.8</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>2010</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21">
+        <v>0.6</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>2020</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22">
+        <v>0.8</v>
+      </c>
+      <c r="E22" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Id</t>
   </si>
@@ -158,6 +158,42 @@
   </si>
   <si>
     <t>debris_cloud_0</t>
+  </si>
+  <si>
+    <t>ACTOR1</t>
+  </si>
+  <si>
+    <t>行雲流水</t>
+  </si>
+  <si>
+    <t>ACTOR2</t>
+  </si>
+  <si>
+    <t>walking</t>
+  </si>
+  <si>
+    <t>ACTOR3</t>
+  </si>
+  <si>
+    <t>ガラバルガ</t>
+  </si>
+  <si>
+    <t>ACTOR4</t>
+  </si>
+  <si>
+    <t>kumomanoyoukou</t>
+  </si>
+  <si>
+    <t>ACTOR5</t>
+  </si>
+  <si>
+    <t>yumemidori</t>
+  </si>
+  <si>
+    <t>ACTOR6</t>
+  </si>
+  <si>
+    <t>kazetami</t>
   </si>
 </sst>
 </file>
@@ -165,10 +201,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -180,28 +216,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -222,6 +259,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -230,15 +282,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,14 +322,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -284,6 +337,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -292,32 +352,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,19 +368,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -356,157 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,6 +559,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -537,6 +597,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -558,24 +633,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,32 +659,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -631,145 +667,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1125,7 +1161,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1511,6 +1547,108 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>3010</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23">
+        <v>0.8</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>3020</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24">
+        <v>0.8</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>3030</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25">
+        <v>0.8</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>3040</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26">
+        <v>0.8</v>
+      </c>
+      <c r="E26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>3050</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27">
+        <v>0.8</v>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>3060</v>
+      </c>
+      <c r="B28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28">
+        <v>0.8</v>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
